--- a/artfynd/A 55334-2025 artfynd.xlsx
+++ b/artfynd/A 55334-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118481119</v>
       </c>
       <c r="B2" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118481173</v>
+        <v>118480312</v>
       </c>
       <c r="B3" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585471</v>
+        <v>585790</v>
       </c>
       <c r="R3" t="n">
-        <v>7060312</v>
+        <v>7060116</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +840,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118480885</v>
+        <v>118480270</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +915,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585514</v>
+        <v>585825</v>
       </c>
       <c r="R4" t="n">
-        <v>7060272</v>
+        <v>7060103</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118481013</v>
+        <v>118480755</v>
       </c>
       <c r="B5" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,22 +1022,22 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585433</v>
+        <v>585567</v>
       </c>
       <c r="R5" t="n">
-        <v>7060346</v>
+        <v>7060175</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,9 +1064,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,65 +1091,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118481322</v>
+        <v>118480885</v>
       </c>
       <c r="B6" t="n">
-        <v>97759</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585529</v>
+        <v>585514</v>
       </c>
       <c r="R6" t="n">
-        <v>7060226</v>
+        <v>7060272</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,9 +1176,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,44 +1203,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118481330</v>
+        <v>118481013</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1238,29 +1243,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585518</v>
+        <v>585433</v>
       </c>
       <c r="R7" t="n">
-        <v>7060228</v>
+        <v>7060346</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,19 +1288,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,27 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118480312</v>
+        <v>125263554</v>
       </c>
       <c r="B8" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,37 +1328,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585790</v>
+        <v>585767</v>
       </c>
       <c r="R8" t="n">
-        <v>7060116</v>
+        <v>7060064</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1387,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,44 +1412,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118480270</v>
+        <v>118481330</v>
       </c>
       <c r="B9" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1471,22 +1452,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585825</v>
+        <v>585518</v>
       </c>
       <c r="R9" t="n">
-        <v>7060103</v>
+        <v>7060228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,12 +1543,7 @@
         <v>118480911</v>
       </c>
       <c r="B10" t="n">
-        <v>97772</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1571,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1654,6 +1634,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118481322</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585529</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7060226</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55334-2025 artfynd.xlsx
+++ b/artfynd/A 55334-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118480312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118480270</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118480755</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118480885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125263554</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481330</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118480911</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,8 +1781,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118481322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>